--- a/stories/arbres/TREE-AUT-006.xlsx
+++ b/stories/arbres/TREE-AUT-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est dans la cuisine, avec papa. Maman plie un linge. Bientôt on part. Il y a un seau, un manteau, un doudou. Papa dit : on va reprendre ses affaires avant de partir.</t>
+          <t>Inès est dans la cuisine, avec papa. Maman plie un linge. Bientôt on part. Il y a un seau, un manteau, un doudou. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est dans la cuisine, avec papa. Maman plie un linge. Bientôt on part. Il y a un seau, un manteau, un doudou.
+papa|On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un gant est près du bol. Papa dit : prends-le.</t>
+          <t>C'est le matin. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un gant est près du bol. Prends-le.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un gant est près du bol.
+papa|Prends-le.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de partir, on reprend ses affaires ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès respire. Papa est là. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2227,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la cuisine. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Inès caresse le doudou. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. On écoute jusqu'au bout. Inès chuchote : c'est fini. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de le matin. Et de la cuisine. Et de le doudou. La lumière est claire. Inès pose la cuisine à sa place. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3616,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la cuisine. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa dit : je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Inès va dans la cuisine. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3754,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la cuisine. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir.
+papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3946,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4113,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Inès s'arrête. Une cloche tinte, tout loin. Inès ferme la porte, tout doux. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le jardin. le seau bleu reste près de le matin. Les chaussures font toc toc. Inès pose sa tête un moment. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4643,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la cuisine. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une chaussette est encore sablée. Inès souffle, puis sourit à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Inès pose la chambre. le matin est derrière. Une tasse cliquette. Inès ferme le sac. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre le doudou. Papa a vu le matin. Et la chambre. Un ballon s'immobilise. Inès serre la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6475,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chapeau est sur la chaise. Maman l'appelle.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6660,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On reprend quoi, avant de partir ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6833,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès retient le geste. Papa sourit. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7024,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7053,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans le jardin. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa dit : je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Inès va dans le jardin. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7191,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans le jardin. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir.
+papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7383,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7550,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un crochet tient bien le manteau. Inès plie un pull. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7717,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7884,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Inès boit une gorgée d'eau. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8051,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8218,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de après la sieste. Et de la cuisine. Et de le doudou. On dit merci. Inès range après la sieste dans sa tête, comme un souvenir. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8385,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8552,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans le jardin. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8743,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8910,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Inès s'arrête. On souffle doucement. Inès marche près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9077,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9244,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le jardin. le seau bleu reste près de après la sieste. On attend son tour. Maman n'est pas loin. Inès les rejoint. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9411,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9440,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9578,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9745,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9912,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans le jardin. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10103,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10270,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un ruban reste dans la poche. Inès range la tasse. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10437,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10604,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Inès pose la chambre. après la sieste est derrière. La couverture est douce. Inès sourit. Papa sourit aussi. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10771,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10938,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre le doudou. Papa a vu après la sieste. Et la chambre. Le vent est doux. Inès essuie ses mains. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11105,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11134,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chausson est sous la table. Papa dit : on les reprend.</t>
+          <t>C'est le soir. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chausson est sous la table. On les reprend.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11272,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chausson est sous la table.
+papa|On les reprend.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On part, et les affaires ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès hoche la tête. On continue, avec papa. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11822,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11989,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la chambre. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12180,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12347,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le soir. Puis la cuisine. Puis le ballon rouge. Un panier est posé sur le banc. Inès range encore un peu, près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12514,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12681,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un vélo passe au loin. Inès tend le seau bleu à maman. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de le soir. Et de la cuisine. Et de le doudou. Ça sent le pain chaud. Inès raccroche un linge. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13182,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13349,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la chambre. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13540,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13569,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de le soir. Inès s'arrête. Un chat miaule une fois. Inès dit : j'ai appris. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Avec le ballon rouge. Après le jardin. Près de le soir. Inès s'arrête. Un chat miaule une fois. J'ai appris. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13707,13 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Inès s'arrête. Un chat miaule une fois.
+enfant-f|J'ai appris. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires.
+narrateur|Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13876,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14043,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le jardin. le seau bleu reste près de le soir. On se tient la main. Inès montre le seau bleu à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14210,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13835,7 +14239,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13973,6 +14377,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14544,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14573,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la chambre. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa dit : je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Inès va dans la chambre. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14711,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va dans la chambre. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir.
+papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14903,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15070,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Inès écoute papa encore une fois. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15237,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15404,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Inès pose la chambre. le soir est derrière. On entend un oiseau. Inès prend la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15571,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15738,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre le doudou. Papa a vu le soir. Et la chambre. Une pomme brille un peu. Inès enfile ses chaussons. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15905,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15945,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-006.xlsx
+++ b/stories/arbres/TREE-AUT-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 papa|Prends-le.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Avant de partir, on reprend ses affaires ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès respire. Papa est là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Inès va dans la cuisine. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Inès a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Inès caresse le doudou. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. On écoute jusqu'au bout. Inès chuchote : c'est fini. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Inès se souvient de le matin. Et de la cuisine. Et de le doudou. La lumière est claire. Inès pose la cuisine à sa place. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
 papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3951,6 +3971,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4118,6 +4139,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Inès s'arrête. Une cloche tinte, tout loin. Inès ferme la porte, tout doux. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4475,7 @@
           <t>narrateur|Inès range le jardin. le seau bleu reste près de le matin. Les chaussures font toc toc. Inès pose sa tête un moment. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4811,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
           <t>narrateur|Inès va dans la cuisine. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5478,6 +5507,7 @@
           <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une chaussette est encore sablée. Inès souffle, puis sourit à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5843,7 @@
           <t>narrateur|Près de le seau bleu. Inès pose la chambre. le matin est derrière. Une tasse cliquette. Inès ferme le sac. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6179,7 @@
           <t>narrateur|Inès montre le doudou. Papa a vu le matin. Et la chambre. Un ballon s'immobilise. Inès serre la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6480,6 +6515,7 @@
           <t>narrateur|C'est après la sieste. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chapeau est sur la chaise. Maman l'appelle.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6667,6 +6703,7 @@
           <t>narrateur|On reprend quoi, avant de partir ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6838,6 +6875,7 @@
           <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès retient le geste. Papa sourit. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7029,6 +7067,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
 papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7388,6 +7428,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7555,6 +7596,7 @@
           <t>narrateur|Inès a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un crochet tient bien le manteau. Inès plie un pull. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7722,6 +7764,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7889,6 +7932,7 @@
           <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Inès boit une gorgée d'eau. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8056,6 +8100,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8223,6 +8268,7 @@
           <t>narrateur|Inès se souvient de après la sieste. Et de la cuisine. Et de le doudou. On dit merci. Inès range après la sieste dans sa tête, comme un souvenir. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8390,6 +8436,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8557,6 +8604,7 @@
           <t>narrateur|Inès va dans le jardin. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8748,6 +8796,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8915,6 +8964,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Inès s'arrête. On souffle doucement. Inès marche près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9082,6 +9132,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9249,6 +9300,7 @@
           <t>narrateur|Inès range le jardin. le seau bleu reste près de après la sieste. On attend son tour. Maman n'est pas loin. Inès les rejoint. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9416,6 +9468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9583,6 +9636,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9750,6 +9804,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9917,6 +9972,7 @@
           <t>narrateur|Inès va dans le jardin. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10108,6 +10164,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10275,6 +10332,7 @@
           <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un ruban reste dans la poche. Inès range la tasse. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10500,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10609,6 +10668,7 @@
           <t>narrateur|Près de le seau bleu. Inès pose la chambre. après la sieste est derrière. La couverture est douce. Inès sourit. Papa sourit aussi. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10776,6 +10836,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10943,6 +11004,7 @@
           <t>narrateur|Inès montre le doudou. Papa a vu après la sieste. Et la chambre. Le vent est doux. Inès essuie ses mains. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11110,6 +11172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11278,6 +11341,7 @@
 papa|On les reprend.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11529,7 @@
           <t>narrateur|On part, et les affaires ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11701,7 @@
           <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès hoche la tête. On continue, avec papa. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11827,6 +11893,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11994,6 +12061,7 @@
           <t>narrateur|Inès va dans la chambre. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12185,6 +12253,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12352,6 +12421,7 @@
           <t>narrateur|Inès a choisi le soir. Puis la cuisine. Puis le ballon rouge. Un panier est posé sur le banc. Inès range encore un peu, près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12519,6 +12589,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12686,6 +12757,7 @@
           <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un vélo passe au loin. Inès tend le seau bleu à maman. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12853,6 +12925,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13020,6 +13093,7 @@
           <t>narrateur|Inès se souvient de le soir. Et de la cuisine. Et de le doudou. Ça sent le pain chaud. Inès raccroche un linge. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13187,6 +13261,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13354,6 +13429,7 @@
           <t>narrateur|Inès va dans la chambre. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13545,6 +13621,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13714,6 +13791,7 @@
 narrateur|Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13881,6 +13959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14048,6 +14127,7 @@
           <t>narrateur|Inès range le jardin. le seau bleu reste près de le soir. On se tient la main. Inès montre le seau bleu à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14215,6 +14295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14382,6 +14463,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14549,6 +14631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14717,6 +14800,7 @@
 papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14908,6 +14992,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15075,6 +15160,7 @@
           <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Inès écoute papa encore une fois. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15242,6 +15328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15409,6 +15496,7 @@
           <t>narrateur|Près de le seau bleu. Inès pose la chambre. le soir est derrière. On entend un oiseau. Inès prend la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15576,6 +15664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15743,6 +15832,7 @@
           <t>narrateur|Inès montre le doudou. Papa a vu le soir. Et la chambre. Une pomme brille un peu. Inès enfile ses chaussons. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15910,6 +16000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15928,7 +16019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15952,6 +16043,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15966,7 +16071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16153,6 +16258,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-006.xlsx
+++ b/stories/arbres/TREE-AUT-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — dans la cuisine</t>
+          <t>Le manteau jaune de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina va bientôt sortir. Le manteau jaune pend. Le seau attend. Elle cherche ses affaires dans la maison, puis elle les reprend avant de partir.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est dans la cuisine, avec papa. Maman plie un linge. Bientôt on part. Il y a un seau, un manteau, un doudou. On va reprendre ses affaires avant de partir.</t>
+          <t>La vitre de la cuisine est un peu embuée. Ça sent la soupe, tout doux. Un manteau jaune pend au crochet. Sous la table, un seau bleu attend. Dehors, la rue est calme. Les chaussures de Nina sèchent près de la porte. On va bientôt sortir, Nina. Tes affaires sont dans la maison. Où est mon seau ? On le cherche ensemble. Une goutte glisse sur la vitre. En ce moment, Nina regarde autour d'elle. Elle veut retrouver ses affaires. On reprend ses affaires avant de partir. Tu es prête à chercher ? Oui, papa. Nina touche le manteau jaune. Il est encore un peu chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,31 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès est dans la cuisine, avec papa. Maman plie un linge. Bientôt on part. Il y a un seau, un manteau, un doudou.
-papa|On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est un peu embuée.
+narrateur|Ça sent la soupe, tout doux.
+narrateur|Un manteau jaune pend au crochet.
+narrateur|Sous la table, un seau bleu attend.
+narrateur|Dehors, la rue est calme.
+narrateur|Les chaussures de Nina sèchent près de la porte.
+maman|On va bientôt sortir, Nina.
+papa|Tes affaires sont dans la maison.
+enfant-f|Où est mon seau ?
+papa|On le cherche ensemble.
+narrateur|Une goutte glisse sur la vitre.
+narrateur|En ce moment, Nina regarde autour d'elle.
+narrateur|Elle veut retrouver ses affaires.
+maman|On reprend ses affaires avant de partir.
+papa|Tu es prête à chercher ?
+enfant-f|Oui, papa.
+narrateur|Nina touche le manteau jaune.
+narrateur|Il est encore un peu chaud.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>soupe,porte,veste</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1386,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1550,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+papa|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un gant est près du bol. Prends-le.</t>
+          <t>C'est le matin. La lumière est claire sur la table. Nina cherche dans la cuisine. Un gant est près du bol. Prends le gant, Nina. Nina le met dans la poche du manteau. On reprend ses affaires avant de partir. Le seau aussi ? Oui. Le seau et le manteau. Nina regarde sous la table. Tu as pris le gant ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,11 +1719,27 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un gant est près du bol.
-papa|Prends-le.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire sur la table.
+narrateur|Nina cherche dans la cuisine.
+narrateur|Un gant est près du bol.
+papa|Prends le gant, Nina.
+narrateur|Nina le met dans la poche du manteau.
+maman|On reprend ses affaires avant de partir.
+enfant-f|Le seau aussi ?
+papa|Oui. Le seau et le manteau.
+narrateur|Nina regarde sous la table.
+maman|Tu as pris le gant ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>bol,gant</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1903,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On va reprendre ses affaires avant de partir. Inès respire. Papa est là. On va reprendre ses affaires avant de partir.</t>
+          <t>Oui. On reprend ses affaires avant de partir. Nina respire, tout calme. Bravo, Nina. Tu as bien écouté. On cherche le seau et le manteau. On les prend.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2047,7 +2096,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès respire. Papa est là. On va reprendre ses affaires avant de partir.</t>
+          <t>narrateur|Oui.
+papa|On reprend ses affaires avant de partir.
+narrateur|Nina respire, tout calme.
+maman|Bravo, Nina.
+maman|Tu as bien écouté.
+papa|On cherche le seau et le manteau.
+enfant-f|On les prend.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2075,7 +2130,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Où Nina cherche-t-elle ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2239,7 +2294,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Où Nina cherche-t-elle ?
+maman|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2267,7 +2323,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la cuisine. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina reste dans la cuisine, le matin. Elle trouve le ballon rouge près du bol. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2407,10 +2463,25 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la cuisine. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina reste dans la cuisine, le matin.
+narrateur|Elle trouve le ballon rouge près du bol.
+papa|Prends-le, Nina.
+narrateur|Nina le serre contre elle.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|L'eau coule un tout petit peu.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+narrateur|La cuisine sent encore la soupe.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>eau,cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2435,7 +2506,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2599,7 +2670,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2627,7 +2699,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Inès caresse le doudou. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le ballon rouge est près du bol. L'eau coule, tout petit bruit. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2767,10 +2839,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Inès caresse le doudou. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la cuisine.
+narrateur|Le ballon rouge est près du bol.
+narrateur|L'eau coule, tout petit bruit.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2795,7 +2886,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2935,7 +3026,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2963,7 +3060,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de le seau bleu. la cuisine est rangé. On écoute jusqu'au bout. Inès chuchote : c'est fini. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le seau bleu est sous la table. Une tasse cliquette près de l'évier. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3103,10 +3200,29 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. On écoute jusqu'au bout. Inès chuchote : c'est fini. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la cuisine.
+narrateur|Le seau bleu est sous la table.
+narrateur|Une tasse cliquette près de l'évier.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3131,7 +3247,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3271,7 +3387,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3299,7 +3421,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de le matin. Et de la cuisine. Et de le doudou. La lumière est claire. Inès pose la cuisine à sa place. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le doudou est sur la chaise. Ça sent encore le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3439,10 +3561,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de le matin. Et de la cuisine. Et de le doudou. La lumière est claire. Inès pose la cuisine à sa place. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la cuisine.
+narrateur|Le doudou est sur la chaise.
+narrateur|Ça sent encore le pain chaud.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3467,7 +3608,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3607,7 +3748,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3635,7 +3782,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la cuisine. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans le jardin, le matin. Elle trouve le ballon rouge dans l'herbe. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3775,11 +3922,25 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la cuisine. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir.
-papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina va dans le jardin, le matin.
+narrateur|Elle trouve le ballon rouge dans l'herbe.
+maman|Prends-le, tout doux.
+narrateur|Une feuille touche sa main.
+papa|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+maman|Oui. Avant de partir.
+narrateur|Le vent est doux sur les joues.
+papa|Tu as trouvé ça ?
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Nina revient vers la porte.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>jardin,feuille</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3804,7 +3965,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3968,7 +4129,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3996,7 +4158,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de le matin. Inès s'arrête. Une cloche tinte, tout loin. Inès ferme la porte, tout doux. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le ballon rouge brille dans l'herbe. Une feuille tombe, tout lentement. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4136,10 +4298,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Inès s'arrête. Une cloche tinte, tout loin. Inès ferme la porte, tout doux. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans le jardin.
+narrateur|Le ballon rouge brille dans l'herbe.
+narrateur|Une feuille tombe, tout lentement.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4164,7 +4345,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4304,7 +4485,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4332,7 +4519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inès range le jardin. le seau bleu reste près de le matin. Les chaussures font toc toc. Inès pose sa tête un moment. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le seau bleu est près des fleurs. Le vent est doux sur les mains. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4472,10 +4659,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le jardin. le seau bleu reste près de le matin. Les chaussures font toc toc. Inès pose sa tête un moment. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans le jardin.
+narrateur|Le seau bleu est près des fleurs.
+narrateur|Le vent est doux sur les mains.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4500,7 +4706,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4640,7 +4846,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4668,7 +4880,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le doudou attend sur le banc de bois. Un oiseau chante une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4808,10 +5020,29 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. Le savon sent bon. Inès répète tout bas le geste. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans le jardin.
+narrateur|Le doudou attend sur le banc de bois.
+narrateur|Un oiseau chante une fois.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4836,7 +5067,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4976,7 +5207,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5004,7 +5241,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la cuisine. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans la chambre, le matin. Elle trouve le ballon rouge sous le lit. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5144,10 +5381,25 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la cuisine. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nina va dans la chambre, le matin.
+narrateur|Elle trouve le ballon rouge sous le lit.
+papa|Prends-le, Nina.
+narrateur|La couverture est encore un peu chaude.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|Nina marche vers le couloir.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>chambre,couverture</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5172,7 +5424,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5336,7 +5588,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5364,7 +5617,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une chaussette est encore sablée. Inès souffle, puis sourit à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le ballon rouge est sous le lit. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5504,10 +5757,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le matin est fini. Une chaussette est encore sablée. Inès souffle, puis sourit à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la chambre.
+narrateur|Le ballon rouge est sous le lit.
+narrateur|Le sol est un peu froid.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5532,7 +5804,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5672,7 +5944,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5700,7 +5978,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Inès pose la chambre. le matin est derrière. Une tasse cliquette. Inès ferme le sac. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le seau bleu est près de l'armoire. Une chaussette est encore sur le tapis. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5840,10 +6118,29 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Inès pose la chambre. le matin est derrière. Une tasse cliquette. Inès ferme le sac. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la chambre.
+narrateur|Le seau bleu est près de l'armoire.
+narrateur|Une chaussette est encore sur le tapis.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5868,7 +6165,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6008,7 +6305,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6036,7 +6339,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Inès montre le doudou. Papa a vu le matin. Et la chambre. Un ballon s'immobilise. Inès serre la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le doudou est sur l'oreiller. La couverture est douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6176,10 +6479,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre le doudou. Papa a vu le matin. Et la chambre. Un ballon s'immobilise. Inès serre la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le matin, dans la chambre.
+narrateur|Le doudou est sur l'oreiller.
+narrateur|La couverture est douce.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le matin, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6204,7 +6526,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6344,7 +6666,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6372,7 +6700,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chapeau est sur la chaise. Maman l'appelle.</t>
+          <t>C'est après la sieste. Les joues de Nina sont encore chaudes. Elle cherche dans la cuisine. Un chapeau est sur la chaise. Prends le chapeau, Nina. Nina le met sur sa tête, tout droit. On reprend ses affaires avant de partir. Où est le manteau ? Au crochet, près de la porte. Nina va vers le crochet. Tu as pris le chapeau ? Oui, papa. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6512,10 +6840,27 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chapeau est sur la chaise. Maman l'appelle.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Nina sont encore chaudes.
+narrateur|Elle cherche dans la cuisine.
+narrateur|Un chapeau est sur la chaise.
+maman|Prends le chapeau, Nina.
+narrateur|Nina le met sur sa tête, tout droit.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Où est le manteau ?
+maman|Au crochet, près de la porte.
+narrateur|Nina va vers le crochet.
+papa|Tu as pris le chapeau ?
+enfant-f|Oui, papa.
+maman|Bravo.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chaise,chapeau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6728,7 +7073,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On va reprendre ses affaires avant de partir. Inès retient le geste. Papa sourit. On va reprendre ses affaires avant de partir.</t>
+          <t>Oui. Le seau et le manteau. On les reprend avant de partir. Bravo, Nina. Tu as fait du bon travail. Nina retient les deux mots. Seau. Manteau.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6872,7 +7217,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès retient le geste. Papa sourit. On va reprendre ses affaires avant de partir.</t>
+          <t>narrateur|Oui.
+maman|Le seau et le manteau.
+maman|On les reprend avant de partir.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina retient les deux mots.
+enfant-f|Seau. Manteau.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6900,7 +7251,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Où Nina cherche-t-elle ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7064,7 +7415,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Où Nina cherche-t-elle ?
+maman|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7092,7 +7444,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans le jardin. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina reste dans la cuisine, après la sieste. Elle trouve le seau bleu sous la table. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7232,11 +7584,25 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans le jardin. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir.
-papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina reste dans la cuisine, après la sieste.
+narrateur|Elle trouve le seau bleu sous la table.
+papa|Prends-le, Nina.
+narrateur|Nina le serre contre elle.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|L'eau coule un tout petit peu.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+narrateur|La cuisine sent encore la soupe.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>eau,cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7261,7 +7627,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7425,7 +7791,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7453,7 +7820,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un crochet tient bien le manteau. Inès plie un pull. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le ballon rouge est près du buffet. Un linge sèche à l'air. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7593,10 +7960,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un crochet tient bien le manteau. Inès plie un pull. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina revient dans la cuisine.
+narrateur|Le ballon rouge est près du buffet.
+narrateur|Un linge sèche à l'air.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7621,7 +8007,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7761,7 +8147,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7789,7 +8181,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Inès boit une gorgée d'eau. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le seau bleu est contre le meuble. Nina boit une gorgée d'eau. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7929,10 +8321,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Inès boit une gorgée d'eau. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina revient dans la cuisine.
+narrateur|Le seau bleu est contre le meuble.
+narrateur|Nina boit une gorgée d'eau.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7957,7 +8368,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8097,7 +8508,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8125,7 +8542,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de après la sieste. Et de la cuisine. Et de le doudou. On dit merci. Inès range après la sieste dans sa tête, comme un souvenir. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le doudou est sur ses genoux un moment. La lumière est plus douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8265,10 +8682,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de après la sieste. Et de la cuisine. Et de le doudou. On dit merci. Inès range après la sieste dans sa tête, comme un souvenir. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina revient dans la cuisine.
+narrateur|Le doudou est sur ses genoux un moment.
+narrateur|La lumière est plus douce.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8293,7 +8729,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8433,7 +8869,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8461,7 +8903,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans le jardin. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans le jardin, après la sieste. Elle trouve le seau bleu près des fleurs. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8601,10 +9043,25 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans le jardin. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina va dans le jardin, après la sieste.
+narrateur|Elle trouve le seau bleu près des fleurs.
+maman|Prends-le, tout doux.
+narrateur|Une feuille touche sa main.
+papa|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+maman|Oui. Avant de partir.
+narrateur|Le vent est doux sur les joues.
+papa|Tu as trouvé ça ?
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Nina revient vers la porte.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>jardin,feuille</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8629,7 +9086,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8793,7 +9250,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8821,7 +9279,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de après la sieste. Inès s'arrête. On souffle doucement. Inès marche près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le ballon rouge a roulé près du seau. Nina souffle, tout doux. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8961,10 +9419,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Inès s'arrête. On souffle doucement. Inès marche près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans le jardin.
+narrateur|Le ballon rouge a roulé près du seau.
+narrateur|Nina souffle, tout doux.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8989,7 +9466,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9129,7 +9606,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9157,7 +9640,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Inès range le jardin. le seau bleu reste près de après la sieste. On attend son tour. Maman n'est pas loin. Inès les rejoint. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le seau bleu est encore un peu chaud. Une abeille passe, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9297,10 +9780,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le jardin. le seau bleu reste près de après la sieste. On attend son tour. Maman n'est pas loin. Inès les rejoint. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans le jardin.
+narrateur|Le seau bleu est encore un peu chaud.
+narrateur|Une abeille passe, tout loin.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9325,7 +9827,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9465,7 +9967,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9493,7 +10001,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le doudou est sur le banc, au soleil. Une feuille tremble. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9633,10 +10141,29 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Une feuille tombe. Inès s'assoit près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans le jardin.
+narrateur|Le doudou est sur le banc, au soleil.
+narrateur|Une feuille tremble.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9661,7 +10188,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9801,7 +10328,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9829,7 +10362,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans le jardin. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans la chambre, après la sieste. Elle trouve le seau bleu près de l'armoire. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9969,10 +10502,25 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans le jardin. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nina va dans la chambre, après la sieste.
+narrateur|Elle trouve le seau bleu près de l'armoire.
+papa|Prends-le, Nina.
+narrateur|La couverture est encore un peu chaude.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|Nina marche vers le couloir.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chambre,couverture</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9997,7 +10545,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10161,7 +10709,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10189,7 +10738,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un ruban reste dans la poche. Inès range la tasse. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le ballon rouge est près des chaussons. Un ruban reste dans la poche. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10329,10 +10878,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un ruban reste dans la poche. Inès range la tasse. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans la chambre.
+narrateur|Le ballon rouge est près des chaussons.
+narrateur|Un ruban reste dans la poche.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10357,7 +10925,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10497,7 +11065,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10525,7 +11099,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Inès pose la chambre. après la sieste est derrière. La couverture est douce. Inès sourit. Papa sourit aussi. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le seau bleu est près de la fenêtre. La couverture est encore chaude. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10665,10 +11239,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Inès pose la chambre. après la sieste est derrière. La couverture est douce. Inès sourit. Papa sourit aussi. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans la chambre.
+narrateur|Le seau bleu est près de la fenêtre.
+narrateur|La couverture est encore chaude.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10693,7 +11286,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10833,7 +11426,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10861,7 +11460,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Inès montre le doudou. Papa a vu après la sieste. Et la chambre. Le vent est doux. Inès essuie ses mains. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le doudou sent encore le lit. Le vent est doux derrière le volet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11001,10 +11600,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre le doudou. Papa a vu après la sieste. Et la chambre. Le vent est doux. Inès essuie ses mains. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Après la sieste, Nina va dans la chambre.
+narrateur|Le doudou sent encore le lit.
+narrateur|Le vent est doux derrière le volet.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, après la sieste, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11029,7 +11647,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11169,7 +11787,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11197,7 +11821,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chausson est sous la table. On les reprend.</t>
+          <t>C'est le soir. La petite lampe éclaire la table. Nina cherche dans la cuisine. Un chausson est sous la table. Prends le chausson, Nina. Nina le pose près de l'autre chausson. On reprend ses affaires avant de partir. Le seau est où ? On le cherche. Ensuite le manteau. Nina se baisse, tout doux. Tu as pris le chausson ? Oui, maman. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11337,11 +11961,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Inès cherche dans la cuisine. Elle va reprendre ses affaires avant de partir. Un chausson est sous la table.
-papa|On les reprend.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La petite lampe éclaire la table.
+narrateur|Nina cherche dans la cuisine.
+narrateur|Un chausson est sous la table.
+papa|Prends le chausson, Nina.
+narrateur|Nina le pose près de l'autre chausson.
+maman|On reprend ses affaires avant de partir.
+enfant-f|Le seau est où ?
+papa|On le cherche. Ensuite le manteau.
+narrateur|Nina se baisse, tout doux.
+maman|Tu as pris le chausson ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lampe,chausson</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11366,7 +12005,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On part, et les affaires ?</t>
+          <t>On part. Et les affaires ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11526,7 +12165,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On part, et les affaires ?</t>
+          <t>narrateur|On part. Et les affaires ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11554,7 +12193,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On va reprendre ses affaires avant de partir. Inès hoche la tête. On continue, avec papa. On va reprendre ses affaires avant de partir.</t>
+          <t>Oui. On reprend ses affaires avant de partir. Nina hoche la tête. On continue ensemble. Bravo. Je cherche.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11698,7 +12337,12 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On va reprendre ses affaires avant de partir. Inès hoche la tête. On continue, avec papa. On va reprendre ses affaires avant de partir.</t>
+          <t>narrateur|Oui.
+papa|On reprend ses affaires avant de partir.
+narrateur|Nina hoche la tête.
+maman|On continue ensemble.
+papa|Bravo.
+enfant-f|Je cherche.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11726,7 +12370,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Où Nina cherche-t-elle ? La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11890,7 +12534,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Où Nina cherche-t-elle ?
+maman|La cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11918,7 +12563,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la chambre. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina reste dans la cuisine, le soir. Elle trouve le doudou sur la chaise. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12058,10 +12703,25 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la chambre. Elle trouve le ballon rouge. Elle va reprendre ses affaires avant de partir. Papa reste tout près. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina reste dans la cuisine, le soir.
+narrateur|Elle trouve le doudou sur la chaise.
+papa|Prends-le, Nina.
+narrateur|Nina le serre contre elle.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|L'eau coule un tout petit peu.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+narrateur|La cuisine sent encore la soupe.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>eau,cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12086,7 +12746,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12250,7 +12910,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12278,7 +12939,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi le soir. Puis la cuisine. Puis le ballon rouge. Un panier est posé sur le banc. Inès range encore un peu, près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le ballon rouge est près du panier. Un panier est posé sur le banc. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12418,10 +13079,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi le soir. Puis la cuisine. Puis le ballon rouge. Un panier est posé sur le banc. Inès range encore un peu, près de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la cuisine.
+narrateur|Le ballon rouge est près du panier.
+narrateur|Un panier est posé sur le banc.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12446,7 +13126,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12586,7 +13266,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12614,7 +13300,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de le seau bleu. la cuisine est rangé. Un vélo passe au loin. Inès tend le seau bleu à maman. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le seau bleu brille sous la lampe. Nina tend le seau à maman. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12754,10 +13440,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de le seau bleu. la cuisine est rangé. Un vélo passe au loin. Inès tend le seau bleu à maman. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la cuisine.
+narrateur|Le seau bleu brille sous la lampe.
+narrateur|Nina tend le seau à maman.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12782,7 +13487,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12922,7 +13627,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12950,7 +13661,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de le soir. Et de la cuisine. Et de le doudou. Ça sent le pain chaud. Inès raccroche un linge. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le doudou est sur la table, tout calme. Ça sent le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13090,10 +13801,29 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de le soir. Et de la cuisine. Et de le doudou. Ça sent le pain chaud. Inès raccroche un linge. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la cuisine.
+narrateur|Le doudou est sur la table, tout calme.
+narrateur|Ça sent le pain chaud.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la cuisine.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13118,7 +13848,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13258,7 +13988,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13286,7 +14022,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la chambre. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans le jardin, le soir. Elle trouve le doudou sur le banc. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13426,10 +14162,25 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la chambre. Elle trouve le seau bleu. Elle va reprendre ses affaires avant de partir. Papa montre le geste, lentement. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina va dans le jardin, le soir.
+narrateur|Elle trouve le doudou sur le banc.
+maman|Prends-le, tout doux.
+narrateur|Une feuille touche sa main.
+papa|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+maman|Oui. Avant de partir.
+narrateur|Le vent est doux sur les joues.
+papa|Tu as trouvé ça ?
+enfant-f|Oui, papa.
+maman|Bravo.
+narrateur|Nina revient vers la porte.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>jardin,feuille</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13454,7 +14205,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13618,7 +14369,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13646,7 +14398,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le ballon rouge. Après le jardin. Près de le soir. Inès s'arrête. Un chat miaule une fois. J'ai appris. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le ballon rouge ne roule plus. Un chat miaule une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13786,12 +14538,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Inès s'arrête. Un chat miaule une fois.
-enfant-f|J'ai appris. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires.
-narrateur|Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans le jardin.
+narrateur|Le ballon rouge ne roule plus.
+narrateur|Un chat miaule une fois.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13816,7 +14585,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13956,7 +14725,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13984,7 +14759,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Inès range le jardin. le seau bleu reste près de le soir. On se tient la main. Inès montre le seau bleu à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le seau bleu est près du portail. Nina montre le seau à papa. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14124,10 +14899,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le jardin. le seau bleu reste près de le soir. On se tient la main. Inès montre le seau bleu à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans le jardin.
+narrateur|Le seau bleu est près du portail.
+narrateur|Nina montre le seau à papa.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14152,7 +14946,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14292,7 +15086,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14320,7 +15120,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le doudou est sur le banc, à l'ombre. On range encore un objet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14460,10 +15260,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. On range un objet. Inès dit merci à papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans le jardin.
+narrateur|Le doudou est sur le banc, à l'ombre.
+narrateur|On range encore un objet.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis le jardin.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14488,7 +15307,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14628,7 +15447,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14656,7 +15481,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Inès va dans la chambre. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir. Je suis là. On va reprendre ses affaires avant de partir.</t>
+          <t>Nina va dans la chambre, le soir. Elle trouve le doudou sur l'oreiller. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14796,11 +15621,25 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Inès va dans la chambre. Elle trouve le doudou. Elle va reprendre ses affaires avant de partir.
-papa|Je suis là. On va reprendre ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nina va dans la chambre, le soir.
+narrateur|Elle trouve le doudou sur l'oreiller.
+papa|Prends-le, Nina.
+narrateur|La couverture est encore un peu chaude.
+maman|On reprend aussi le seau et le manteau.
+enfant-f|Avant de partir.
+papa|Oui. Avant de partir.
+narrateur|Nina marche vers le couloir.
+maman|Tu as pris ça ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>chambre,couverture</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14825,7 +15664,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Elle emporte aussi quoi ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14989,7 +15828,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Elle emporte aussi quoi ?
+papa|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15017,7 +15857,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Inès écoute papa encore une fois. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le ballon rouge est dans le coffre. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15157,10 +15997,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Inès écoute papa encore une fois. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la chambre.
+narrateur|Le ballon rouge est dans le coffre.
+narrateur|Le sol est un peu froid.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le ballon rouge aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15185,7 +16044,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15325,7 +16184,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le ballon rouge.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15353,7 +16218,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de le seau bleu. Inès pose la chambre. le soir est derrière. On entend un oiseau. Inès prend la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le seau bleu est près de la porte. On entend un oiseau, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15493,10 +16358,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de le seau bleu. Inès pose la chambre. le soir est derrière. On entend un oiseau. Inès prend la main de papa. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la chambre.
+narrateur|Le seau bleu est près de la porte.
+narrateur|On entend un oiseau, tout loin.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le seau bleu aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15521,7 +16405,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15661,7 +16545,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le seau bleu.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15689,7 +16579,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Inès montre le doudou. Papa a vu le soir. Et la chambre. Une pomme brille un peu. Inès enfile ses chaussons. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le doudou est déjà dans ses bras. Une pomme brille un peu sur la commode. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15829,10 +16719,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre le doudou. Papa a vu le soir. Et la chambre. Une pomme brille un peu. Inès enfile ses chaussons. On va reprendre ses affaires avant de partir. On cherche seau et manteau. On les prend. On va reprendre ses affaires. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, Nina cherche dans la chambre.
+narrateur|Le doudou est déjà dans ses bras.
+narrateur|Une pomme brille un peu sur la commode.
+papa|On cherche le seau et le manteau.
+narrateur|Nina regarde. Elle les trouve.
+maman|Prends-les, Nina.
+narrateur|Nina prend le seau. Puis le manteau.
+enfant-f|Et le doudou aussi.
+papa|Oui. On reprend ses affaires avant de partir.
+maman|Tu as tout ?
+enfant-f|Oui, maman.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Ils vont vers la porte, le soir, depuis la chambre.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15857,7 +16766,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15997,7 +16906,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a repris le doudou.
+narrateur|Elle a le seau. Elle a le manteau.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|On reprend ses affaires avant de partir.
+enfant-f|Avant de partir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16019,7 +16934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16057,6 +16972,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-006.xlsx
+++ b/stories/arbres/TREE-AUT-006.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est un peu embuée. Ça sent la soupe, tout doux. Un manteau jaune pend au crochet. Sous la table, un seau bleu attend. Dehors, la rue est calme. Les chaussures de Nina sèchent près de la porte. On va bientôt sortir, Nina. Tes affaires sont dans la maison. Où est mon seau ? On le cherche ensemble. Une goutte glisse sur la vitre. En ce moment, Nina regarde autour d'elle. Elle veut retrouver ses affaires. On reprend ses affaires avant de partir. Tu es prête à chercher ? Oui, papa. Nina touche le manteau jaune. Il est encore un peu chaud.</t>
+          <t>La vitre de la cuisine est un peu embuée. Ça sent la soupe, tout doux. Un manteau jaune pend au crochet. Sous la table, un seau bleu attend. Dehors, la rue est calme. Les chaussures de Nina sèchent près de la porte. On va bientôt sortir, Nina. Tes affaires sont dans la maison. Où est mon seau ? On le cherche ensemble. Une goutte glisse sur la vitre. En ce moment, Nina regarde autour d'elle. Elle veut retrouver ses affaires. On va reprendre ses affaires avant de partir. Tu es prête à chercher ? Oui, papa. Des miettes dorées sont sur la table. Le robinet fait une goutte, puis s'arrête. Tu as vu le manteau jaune ? Oui. Il est chaud. On va le prendre. Ensuite le seau. Nina pose une main sur le crochet. Le bouton du manteau brille. Nina touche le manteau jaune. Il est encore un peu chaud.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1350,9 +1350,17 @@
 narrateur|Une goutte glisse sur la vitre.
 narrateur|En ce moment, Nina regarde autour d'elle.
 narrateur|Elle veut retrouver ses affaires.
-maman|On reprend ses affaires avant de partir.
+maman|On va reprendre ses affaires avant de partir.
 papa|Tu es prête à chercher ?
 enfant-f|Oui, papa.
+narrateur|Des miettes dorées sont sur la table.
+narrateur|Le robinet fait une goutte, puis s'arrête.
+maman|Tu as vu le manteau jaune ?
+enfant-f|Oui. Il est chaud.
+papa|On va le prendre.
+papa|Ensuite le seau.
+narrateur|Nina pose une main sur le crochet.
+narrateur|Le bouton du manteau brille.
 narrateur|Nina touche le manteau jaune.
 narrateur|Il est encore un peu chaud.</t>
         </is>
@@ -1579,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est claire sur la table. Nina cherche dans la cuisine. Un gant est près du bol. Prends le gant, Nina. Nina le met dans la poche du manteau. On reprend ses affaires avant de partir. Le seau aussi ? Oui. Le seau et le manteau. Nina regarde sous la table. Tu as pris le gant ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est claire sur la table. Nina cherche dans la cuisine. Un gant est près du bol. Prends le gant, Nina. Nina le met dans la poche du manteau. On va reprendre ses affaires avant de partir. Le seau aussi ? Oui. Le seau et le manteau. Nina regarde sous la table. Tu as pris le gant ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1725,7 +1733,7 @@
 narrateur|Un gant est près du bol.
 papa|Prends le gant, Nina.
 narrateur|Nina le met dans la poche du manteau.
-maman|On reprend ses affaires avant de partir.
+maman|On va reprendre ses affaires avant de partir.
 enfant-f|Le seau aussi ?
 papa|Oui. Le seau et le manteau.
 narrateur|Nina regarde sous la table.
@@ -1952,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On reprend ses affaires avant de partir. Nina respire, tout calme. Bravo, Nina. Tu as bien écouté. On cherche le seau et le manteau. On les prend.</t>
+          <t>Oui. On va reprendre ses affaires avant de partir. Nina respire, tout calme. Bravo, Nina. Tu as bien écouté. On cherche le seau et le manteau. On les prend.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2097,7 +2105,7 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Oui.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 narrateur|Nina respire, tout calme.
 maman|Bravo, Nina.
 maman|Tu as bien écouté.
@@ -2323,7 +2331,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Nina reste dans la cuisine, le matin. Elle trouve le ballon rouge près du bol. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
+          <t>Nina cherche dans la cuisine, le matin. Elle ouvre le placard, tout doux. Une tasse cliquette. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde sous la table. L'eau coule un tout petit peu. Tu as regardé sous la table ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2463,15 +2471,15 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Nina reste dans la cuisine, le matin.
-narrateur|Elle trouve le ballon rouge près du bol.
-papa|Prends-le, Nina.
-narrateur|Nina le serre contre elle.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
+          <t>narrateur|Nina cherche dans la cuisine, le matin.
+narrateur|Elle ouvre le placard, tout doux.
+narrateur|Une tasse cliquette.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde sous la table.
 narrateur|L'eau coule un tout petit peu.
-maman|Tu as pris ça ?
+maman|Tu as regardé sous la table ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 narrateur|La cuisine sent encore la soupe.</t>
@@ -2699,7 +2707,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la cuisine. Le ballon rouge est près du bol. L'eau coule, tout petit bruit. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le ballon rouge est près du bol. L'eau coule, tout petit bruit. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2847,7 +2855,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -2886,7 +2894,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3030,7 +3038,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3060,7 +3068,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la cuisine. Le seau bleu est sous la table. Une tasse cliquette près de l'évier. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le seau bleu est sous la table. Une tasse cliquette près de l'évier. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3208,7 +3216,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -3247,7 +3255,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3391,7 +3399,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3421,7 +3429,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la cuisine. Le doudou est sur la chaise. Ça sent encore le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la cuisine. Le doudou est sur la chaise. Ça sent encore le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3569,7 +3577,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -3608,7 +3616,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3752,7 +3760,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3782,7 +3790,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans le jardin, le matin. Elle trouve le ballon rouge dans l'herbe. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
+          <t>Nina va dans le jardin, le matin. L'herbe est un peu froide sous les pieds. Une feuille touche sa main. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde près du banc. Le vent est doux sur les joues. Tu as regardé près du banc ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3923,14 +3931,14 @@
       <c r="AW16" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans le jardin, le matin.
-narrateur|Elle trouve le ballon rouge dans l'herbe.
-maman|Prends-le, tout doux.
+narrateur|L'herbe est un peu froide sous les pieds.
 narrateur|Une feuille touche sa main.
-papa|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-maman|Oui. Avant de partir.
+maman|On cherche le seau et le manteau.
+papa|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde près du banc.
 narrateur|Le vent est doux sur les joues.
-papa|Tu as trouvé ça ?
+papa|Tu as regardé près du banc ?
 enfant-f|Oui, papa.
 maman|Bravo.
 narrateur|Nina revient vers la porte.</t>
@@ -4158,7 +4166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans le jardin. Le ballon rouge brille dans l'herbe. Une feuille tombe, tout lentement. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le ballon rouge brille dans l'herbe. Une feuille tombe, tout lentement. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4306,7 +4314,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -4345,7 +4353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4489,7 +4497,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4519,7 +4527,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans le jardin. Le seau bleu est près des fleurs. Le vent est doux sur les mains. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le seau bleu est près des fleurs. Le vent est doux sur les mains. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4667,7 +4675,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -4706,7 +4714,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4850,7 +4858,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4880,7 +4888,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans le jardin. Le doudou attend sur le banc de bois. Un oiseau chante une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans le jardin. Le doudou attend sur le banc de bois. Un oiseau chante une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5028,7 +5036,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -5067,7 +5075,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5211,7 +5219,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5241,7 +5249,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans la chambre, le matin. Elle trouve le ballon rouge sous le lit. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
+          <t>Nina va dans la chambre, le matin. La couverture est encore un peu chaude. Elle regarde près de l'armoire. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina marche vers le couloir, puis revient. Tu as regardé près de l'armoire ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5382,14 +5390,13 @@
       <c r="AW24" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans la chambre, le matin.
-narrateur|Elle trouve le ballon rouge sous le lit.
-papa|Prends-le, Nina.
 narrateur|La couverture est encore un peu chaude.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
-narrateur|Nina marche vers le couloir.
-maman|Tu as pris ça ?
+narrateur|Elle regarde près de l'armoire.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina marche vers le couloir, puis revient.
+maman|Tu as regardé près de l'armoire ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 papa|Tu as fait du bon travail.</t>
@@ -5617,7 +5624,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la chambre. Le ballon rouge est sous le lit. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le ballon rouge est sous le lit. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5765,7 +5772,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -5804,7 +5811,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5948,7 +5955,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5978,7 +5985,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la chambre. Le seau bleu est près de l'armoire. Une chaussette est encore sur le tapis. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le seau bleu est près de l'armoire. Une chaussette est encore sur le tapis. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6126,7 +6133,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -6165,7 +6172,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6309,7 +6316,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6339,7 +6346,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nina a choisi le matin, dans la chambre. Le doudou est sur l'oreiller. La couverture est douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Nina a choisi le matin, dans la chambre. Le doudou est sur l'oreiller. La couverture est douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le matin, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6487,7 +6494,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -6526,7 +6533,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6670,7 +6677,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6700,7 +6707,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Nina sont encore chaudes. Elle cherche dans la cuisine. Un chapeau est sur la chaise. Prends le chapeau, Nina. Nina le met sur sa tête, tout droit. On reprend ses affaires avant de partir. Où est le manteau ? Au crochet, près de la porte. Nina va vers le crochet. Tu as pris le chapeau ? Oui, papa. Bravo. C'est du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Nina sont encore chaudes. Elle cherche dans la cuisine. Un chapeau est sur la chaise. Prends le chapeau, Nina. Nina le met sur sa tête, tout droit. On va reprendre ses affaires avant de partir. Où est le manteau ? Au crochet, près de la porte. Nina va vers le crochet. Tu as pris le chapeau ? Oui, papa. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6846,7 +6853,7 @@
 narrateur|Un chapeau est sur la chaise.
 maman|Prends le chapeau, Nina.
 narrateur|Nina le met sur sa tête, tout droit.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Où est le manteau ?
 maman|Au crochet, près de la porte.
 narrateur|Nina va vers le crochet.
@@ -7073,7 +7080,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Le seau et le manteau. On les reprend avant de partir. Bravo, Nina. Tu as fait du bon travail. Nina retient les deux mots. Seau. Manteau.</t>
+          <t>Oui. Le seau et le manteau. On va reprendre ses affaires avant de partir. Bravo, Nina. Tu as fait du bon travail. Nina retient les deux mots. Seau. Manteau.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -7219,7 +7226,7 @@
         <is>
           <t>narrateur|Oui.
 maman|Le seau et le manteau.
-maman|On les reprend avant de partir.
+maman|On va reprendre ses affaires avant de partir.
 papa|Bravo, Nina.
 papa|Tu as fait du bon travail.
 narrateur|Nina retient les deux mots.
@@ -7444,7 +7451,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nina reste dans la cuisine, après la sieste. Elle trouve le seau bleu sous la table. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
+          <t>Nina cherche dans la cuisine, après la sieste. Elle ouvre le placard, tout doux. Une tasse cliquette. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde sous la table. L'eau coule un tout petit peu. Tu as regardé sous la table ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7584,15 +7591,15 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Nina reste dans la cuisine, après la sieste.
-narrateur|Elle trouve le seau bleu sous la table.
-papa|Prends-le, Nina.
-narrateur|Nina le serre contre elle.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
+          <t>narrateur|Nina cherche dans la cuisine, après la sieste.
+narrateur|Elle ouvre le placard, tout doux.
+narrateur|Une tasse cliquette.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde sous la table.
 narrateur|L'eau coule un tout petit peu.
-maman|Tu as pris ça ?
+maman|Tu as regardé sous la table ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 narrateur|La cuisine sent encore la soupe.</t>
@@ -7820,7 +7827,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina revient dans la cuisine. Le ballon rouge est près du buffet. Un linge sèche à l'air. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le ballon rouge est près du buffet. Un linge sèche à l'air. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7968,7 +7975,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -8007,7 +8014,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8151,7 +8158,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8181,7 +8188,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina revient dans la cuisine. Le seau bleu est contre le meuble. Nina boit une gorgée d'eau. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le seau bleu est contre le meuble. Nina boit une gorgée d'eau. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -8329,7 +8336,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -8368,7 +8375,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8512,7 +8519,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8542,7 +8549,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina revient dans la cuisine. Le doudou est sur ses genoux un moment. La lumière est plus douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina revient dans la cuisine. Le doudou est sur ses genoux un moment. La lumière est plus douce. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8690,7 +8697,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -8729,7 +8736,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8873,7 +8880,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8903,7 +8910,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans le jardin, après la sieste. Elle trouve le seau bleu près des fleurs. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
+          <t>Nina va dans le jardin, après la sieste. L'herbe est un peu froide sous les pieds. Une feuille touche sa main. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde près du banc. Le vent est doux sur les joues. Tu as regardé près du banc ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -9044,14 +9051,14 @@
       <c r="AW44" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans le jardin, après la sieste.
-narrateur|Elle trouve le seau bleu près des fleurs.
-maman|Prends-le, tout doux.
+narrateur|L'herbe est un peu froide sous les pieds.
 narrateur|Une feuille touche sa main.
-papa|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-maman|Oui. Avant de partir.
+maman|On cherche le seau et le manteau.
+papa|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde près du banc.
 narrateur|Le vent est doux sur les joues.
-papa|Tu as trouvé ça ?
+papa|Tu as regardé près du banc ?
 enfant-f|Oui, papa.
 maman|Bravo.
 narrateur|Nina revient vers la porte.</t>
@@ -9279,7 +9286,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans le jardin. Le ballon rouge a roulé près du seau. Nina souffle, tout doux. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le ballon rouge a roulé près du seau. Nina souffle, tout doux. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9427,7 +9434,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -9466,7 +9473,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9610,7 +9617,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -9640,7 +9647,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans le jardin. Le seau bleu est encore un peu chaud. Une abeille passe, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le seau bleu est encore un peu chaud. Une abeille passe, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9788,7 +9795,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -9827,7 +9834,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9971,7 +9978,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -10001,7 +10008,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans le jardin. Le doudou est sur le banc, au soleil. Une feuille tremble. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans le jardin. Le doudou est sur le banc, au soleil. Une feuille tremble. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10149,7 +10156,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -10188,7 +10195,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10332,7 +10339,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -10362,7 +10369,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans la chambre, après la sieste. Elle trouve le seau bleu près de l'armoire. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
+          <t>Nina va dans la chambre, après la sieste. La couverture est encore un peu chaude. Elle regarde près de l'armoire. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina marche vers le couloir, puis revient. Tu as regardé près de l'armoire ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10503,14 +10510,13 @@
       <c r="AW52" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans la chambre, après la sieste.
-narrateur|Elle trouve le seau bleu près de l'armoire.
-papa|Prends-le, Nina.
 narrateur|La couverture est encore un peu chaude.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
-narrateur|Nina marche vers le couloir.
-maman|Tu as pris ça ?
+narrateur|Elle regarde près de l'armoire.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina marche vers le couloir, puis revient.
+maman|Tu as regardé près de l'armoire ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 papa|Tu as fait du bon travail.</t>
@@ -10738,7 +10744,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans la chambre. Le ballon rouge est près des chaussons. Un ruban reste dans la poche. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le ballon rouge est près des chaussons. Un ruban reste dans la poche. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10886,7 +10892,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -10925,7 +10931,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11069,7 +11075,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11099,7 +11105,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans la chambre. Le seau bleu est près de la fenêtre. La couverture est encore chaude. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le seau bleu est près de la fenêtre. La couverture est encore chaude. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11247,7 +11253,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -11286,7 +11292,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11430,7 +11436,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11460,7 +11466,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, Nina va dans la chambre. Le doudou sent encore le lit. Le vent est doux derrière le volet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Après la sieste, Nina va dans la chambre. Le doudou sent encore le lit. Le vent est doux derrière le volet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, après la sieste, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11608,7 +11614,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -11647,7 +11653,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11791,7 +11797,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11821,7 +11827,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La petite lampe éclaire la table. Nina cherche dans la cuisine. Un chausson est sous la table. Prends le chausson, Nina. Nina le pose près de l'autre chausson. On reprend ses affaires avant de partir. Le seau est où ? On le cherche. Ensuite le manteau. Nina se baisse, tout doux. Tu as pris le chausson ? Oui, maman. Bravo, Nina.</t>
+          <t>C'est le soir. La petite lampe éclaire la table. Nina cherche dans la cuisine. Un chausson est sous la table. Prends le chausson, Nina. Nina le pose près de l'autre chausson. On va reprendre ses affaires avant de partir. Le seau est où ? On le cherche. Ensuite le manteau. Nina se baisse, tout doux. Tu as pris le chausson ? Oui, maman. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11967,7 +11973,7 @@
 narrateur|Un chausson est sous la table.
 papa|Prends le chausson, Nina.
 narrateur|Nina le pose près de l'autre chausson.
-maman|On reprend ses affaires avant de partir.
+maman|On va reprendre ses affaires avant de partir.
 enfant-f|Le seau est où ?
 papa|On le cherche. Ensuite le manteau.
 narrateur|Nina se baisse, tout doux.
@@ -12193,7 +12199,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On reprend ses affaires avant de partir. Nina hoche la tête. On continue ensemble. Bravo. Je cherche.</t>
+          <t>Oui. On va reprendre ses affaires avant de partir. Nina hoche la tête. On continue ensemble. Bravo. Je cherche.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -12338,7 +12344,7 @@
       <c r="AW62" t="inlineStr">
         <is>
           <t>narrateur|Oui.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 narrateur|Nina hoche la tête.
 maman|On continue ensemble.
 papa|Bravo.
@@ -12563,7 +12569,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Nina reste dans la cuisine, le soir. Elle trouve le doudou sur la chaise. Prends-le, Nina. Nina le serre contre elle. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. L'eau coule un tout petit peu. Tu as pris ça ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
+          <t>Nina cherche dans la cuisine, le soir. Elle ouvre le placard, tout doux. Une tasse cliquette. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde sous la table. L'eau coule un tout petit peu. Tu as regardé sous la table ? Oui, maman. Bravo, Nina. La cuisine sent encore la soupe.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12703,15 +12709,15 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Nina reste dans la cuisine, le soir.
-narrateur|Elle trouve le doudou sur la chaise.
-papa|Prends-le, Nina.
-narrateur|Nina le serre contre elle.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
+          <t>narrateur|Nina cherche dans la cuisine, le soir.
+narrateur|Elle ouvre le placard, tout doux.
+narrateur|Une tasse cliquette.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde sous la table.
 narrateur|L'eau coule un tout petit peu.
-maman|Tu as pris ça ?
+maman|Tu as regardé sous la table ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 narrateur|La cuisine sent encore la soupe.</t>
@@ -12939,7 +12945,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la cuisine. Le ballon rouge est près du panier. Un panier est posé sur le banc. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le ballon rouge est près du panier. Un panier est posé sur le banc. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -13087,7 +13093,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -13126,7 +13132,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13270,7 +13276,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13300,7 +13306,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la cuisine. Le seau bleu brille sous la lampe. Nina tend le seau à maman. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le seau bleu brille sous la lampe. Nina tend le seau à maman. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13448,7 +13454,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -13487,7 +13493,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13631,7 +13637,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13661,7 +13667,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la cuisine. Le doudou est sur la table, tout calme. Ça sent le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la cuisine. Le doudou est sur la table, tout calme. Ça sent le pain chaud. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la cuisine. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13809,7 +13815,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -13848,7 +13854,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13992,7 +13998,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14022,7 +14028,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans le jardin, le soir. Elle trouve le doudou sur le banc. Prends-le, tout doux. Une feuille touche sa main. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Le vent est doux sur les joues. Tu as trouvé ça ? Oui, papa. Bravo. Nina revient vers la porte.</t>
+          <t>Nina va dans le jardin, le soir. L'herbe est un peu froide sous les pieds. Une feuille touche sa main. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina regarde près du banc. Le vent est doux sur les joues. Tu as regardé près du banc ? Oui, papa. Bravo. Nina revient vers la porte.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -14163,14 +14169,14 @@
       <c r="AW72" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans le jardin, le soir.
-narrateur|Elle trouve le doudou sur le banc.
-maman|Prends-le, tout doux.
+narrateur|L'herbe est un peu froide sous les pieds.
 narrateur|Une feuille touche sa main.
-papa|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-maman|Oui. Avant de partir.
+maman|On cherche le seau et le manteau.
+papa|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina regarde près du banc.
 narrateur|Le vent est doux sur les joues.
-papa|Tu as trouvé ça ?
+papa|Tu as regardé près du banc ?
 enfant-f|Oui, papa.
 maman|Bravo.
 narrateur|Nina revient vers la porte.</t>
@@ -14398,7 +14404,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans le jardin. Le ballon rouge ne roule plus. Un chat miaule une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le ballon rouge ne roule plus. Un chat miaule une fois. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14546,7 +14552,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -14585,7 +14591,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14729,7 +14735,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14759,7 +14765,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans le jardin. Le seau bleu est près du portail. Nina montre le seau à papa. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le seau bleu est près du portail. Nina montre le seau à papa. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14907,7 +14913,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -14946,7 +14952,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -15090,7 +15096,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -15120,7 +15126,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans le jardin. Le doudou est sur le banc, à l'ombre. On range encore un objet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans le jardin. Le doudou est sur le banc, à l'ombre. On range encore un objet. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis le jardin. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15268,7 +15274,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -15307,7 +15313,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15451,7 +15457,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -15481,7 +15487,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nina va dans la chambre, le soir. Elle trouve le doudou sur l'oreiller. Prends-le, Nina. La couverture est encore un peu chaude. On reprend aussi le seau et le manteau. Avant de partir. Oui. Avant de partir. Nina marche vers le couloir. Tu as pris ça ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
+          <t>Nina va dans la chambre, le soir. La couverture est encore un peu chaude. Elle regarde près de l'armoire. On cherche le seau et le manteau. On les prend avant de partir. Je cherche. Nina marche vers le couloir, puis revient. Tu as regardé près de l'armoire ? Oui, maman. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -15622,14 +15628,13 @@
       <c r="AW80" t="inlineStr">
         <is>
           <t>narrateur|Nina va dans la chambre, le soir.
-narrateur|Elle trouve le doudou sur l'oreiller.
-papa|Prends-le, Nina.
 narrateur|La couverture est encore un peu chaude.
-maman|On reprend aussi le seau et le manteau.
-enfant-f|Avant de partir.
-papa|Oui. Avant de partir.
-narrateur|Nina marche vers le couloir.
-maman|Tu as pris ça ?
+narrateur|Elle regarde près de l'armoire.
+papa|On cherche le seau et le manteau.
+maman|On les prend avant de partir.
+enfant-f|Je cherche.
+narrateur|Nina marche vers le couloir, puis revient.
+maman|Tu as regardé près de l'armoire ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
 papa|Tu as fait du bon travail.</t>
@@ -15857,7 +15862,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la chambre. Le ballon rouge est dans le coffre. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le ballon rouge est dans le coffre. Le sol est un peu froid. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le ballon rouge aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -16005,7 +16010,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le ballon rouge aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -16044,7 +16049,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le ballon rouge. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16188,7 +16193,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16218,7 +16223,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la chambre. Le seau bleu est près de la porte. On entend un oiseau, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le seau bleu est près de la porte. On entend un oiseau, tout loin. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le seau bleu aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16366,7 +16371,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le seau bleu aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -16405,7 +16410,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le seau bleu. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16549,7 +16554,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16579,7 +16584,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nina cherche dans la chambre. Le doudou est déjà dans ses bras. Une pomme brille un peu sur la commode. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On reprend ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
+          <t>Le soir, Nina cherche dans la chambre. Le doudou est déjà dans ses bras. Une pomme brille un peu sur la commode. On cherche le seau et le manteau. Nina regarde. Elle les trouve. Prends-les, Nina. Nina prend le seau. Puis le manteau. Et le doudou aussi. Oui. On va reprendre ses affaires avant de partir. Tu as tout ? Oui, maman. Bravo, Nina. Tu as fait du bon travail. Ils vont vers la porte, le soir, depuis la chambre. Merci, papa. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16727,7 +16732,7 @@
 maman|Prends-les, Nina.
 narrateur|Nina prend le seau. Puis le manteau.
 enfant-f|Et le doudou aussi.
-papa|Oui. On reprend ses affaires avant de partir.
+papa|Oui. On va reprendre ses affaires avant de partir.
 maman|Tu as tout ?
 enfant-f|Oui, maman.
 papa|Bravo, Nina.
@@ -16766,7 +16771,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On reprend ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
+          <t>Nina a repris le doudou. Elle a le seau. Elle a le manteau. Bravo, Nina. Tu as fait du bon travail. On va reprendre ses affaires avant de partir. Avant de partir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16910,7 +16915,7 @@
 narrateur|Elle a le seau. Elle a le manteau.
 maman|Bravo, Nina.
 maman|Tu as fait du bon travail.
-papa|On reprend ses affaires avant de partir.
+papa|On va reprendre ses affaires avant de partir.
 enfant-f|Avant de partir.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16934,7 +16939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16977,6 +16982,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
